--- a/Mandat 1 - Planification/BelleVibe MatricePermissions.xlsx
+++ b/Mandat 1 - Planification/BelleVibe MatricePermissions.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmaisonneuveqcca-my.sharepoint.com/personal/e6302453_cmaisonneuve_qc_ca/Documents/Session 4/Projet 2/BelleVibe/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_DE1BCBCCDAD57945D02AE09552928C776C0C3DF9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{391B1EBC-7DCD-4540-8A6C-D4823147CBB3}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
@@ -22,92 +27,89 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="26">
   <si>
-    <t xml:space="preserve">Employés</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Superviseur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clients</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Read</t>
-  </si>
-  <si>
-    <t xml:space="preserve">✓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Permissions standard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Write</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seul les superviseurs et les admins peuvent voir les autres employés. Les admins peuvent modifier le statut/position d'un employé (passer de simple employé à superviseur ex). Les superviseurs peuvent modifier les autres infos (ex, changement d'adresse)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comptes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Historique des dossiers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La table "historique des dossiers" se rempli automatiquement dès qu'une action est faite partout dans le système. Seul les superviseurs et admins ont accès à sa lecture mais aucune modification, écriture ou suppréssion est possible.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dossiers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seul les admins peuvent supprimer des notes, puisqu'elles servent seulement à garder des commentaires ou des remarques sur les clients donc il serait très rare de devoir les supprimer en tant que superviseur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demandes</t>
+    <t>Employés</t>
+  </si>
+  <si>
+    <t>Superviseur</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Clients</t>
+  </si>
+  <si>
+    <t>Read</t>
+  </si>
+  <si>
+    <t>✓</t>
+  </si>
+  <si>
+    <t>Permissions standard</t>
+  </si>
+  <si>
+    <t>Write</t>
+  </si>
+  <si>
+    <t>Edit</t>
+  </si>
+  <si>
+    <t>Delete</t>
+  </si>
+  <si>
+    <t>Seul les superviseurs et les admins peuvent voir les autres employés. Les admins peuvent modifier le statut/position d'un employé (passer de simple employé à superviseur ex). Les superviseurs peuvent modifier les autres infos (ex, changement d'adresse)</t>
+  </si>
+  <si>
+    <t>Comptes</t>
+  </si>
+  <si>
+    <t>Historique des dossiers</t>
+  </si>
+  <si>
+    <t>La table "historique des dossiers" se rempli automatiquement dès qu'une action est faite partout dans le système. Seul les superviseurs et admins ont accès à sa lecture mais aucune modification, écriture ou suppréssion est possible.</t>
+  </si>
+  <si>
+    <t>Dossiers</t>
+  </si>
+  <si>
+    <t>Seul les admins peuvent supprimer des notes, puisqu'elles servent seulement à garder des commentaires ou des remarques sur les clients donc il serait très rare de devoir les supprimer en tant que superviseur</t>
+  </si>
+  <si>
+    <t>Demandes</t>
   </si>
   <si>
     <t xml:space="preserve">Les employés devraient seulement écrire et lire les demandes que les clients leur font parvenir. Si on doit en modifier une (ex, l'état de la demande) un superviseur s'en charge. </t>
   </si>
   <si>
-    <t xml:space="preserve">Documents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forfait Dossier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lorsqu’un client appèle, on veut que l’employé puisse voir les forfaits déjà à son dossier, ajouter un nouveau forfait, modifier les forfaits en cours, ou même supprimer un forfait du dossier du client sans avoir à avoir affaire avec un superviseur ou un admin.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forfaits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Les employés et les superviseurs peuvent voir les forfaits disponnibles mais seul un admin devrait avoir le droit de modifier, supprimer ou créer de nouveaux forfaits.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Les employés et les superviseurs peuvent voir les services mais seul un admin devrait avoir d’autres droit sur cette table.</t>
+    <t>Documents</t>
+  </si>
+  <si>
+    <t>Forfait Dossier</t>
+  </si>
+  <si>
+    <t>Lorsqu’un client appèle, on veut que l’employé puisse voir les forfaits déjà à son dossier, ajouter un nouveau forfait, modifier les forfaits en cours, ou même supprimer un forfait du dossier du client sans avoir à avoir affaire avec un superviseur ou un admin.</t>
+  </si>
+  <si>
+    <t>Forfaits</t>
+  </si>
+  <si>
+    <t>Les employés et les superviseurs peuvent voir les forfaits disponnibles mais seul un admin devrait avoir le droit de modifier, supprimer ou créer de nouveaux forfaits.</t>
+  </si>
+  <si>
+    <t>Services</t>
+  </si>
+  <si>
+    <t>Les employés et les superviseurs peuvent voir les services mais seul un admin devrait avoir d’autres droit sur cette table.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -115,22 +117,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="14"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -143,14 +130,14 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="22"/>
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="14"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -165,150 +152,129 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="LibreOffice">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -361,44 +327,43 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:XFD45"/>
-  <sheetFormatPr defaultColWidth="10.5703125" defaultRowHeight="28.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.5703125" defaultRowHeight="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.57"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="10.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="2" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="43.29"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="2" width="10.57"/>
+    <col min="1" max="1" width="16.5703125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" style="4"/>
+    <col min="3" max="5" width="11.7109375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="43.28515625" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="10.5703125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C1" s="4" t="s">
+    <row r="1" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+      <c r="N1" s="3"/>
+    </row>
+    <row r="2" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="6" t="s">
@@ -410,15 +375,15 @@
       <c r="E2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5"/>
-      <c r="B3" s="4" t="s">
+    <row r="3" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2"/>
+      <c r="B3" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C3" s="6" t="s">
@@ -430,11 +395,11 @@
       <c r="E3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="4"/>
-    </row>
-    <row r="4" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5"/>
-      <c r="B4" s="4" t="s">
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2"/>
+      <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="6" t="s">
@@ -446,11 +411,11 @@
       <c r="E4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5"/>
-      <c r="B5" s="4" t="s">
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2"/>
+      <c r="B5" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="6"/>
@@ -460,13 +425,13 @@
       <c r="E5" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="4"/>
-    </row>
-    <row r="6" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="6"/>
@@ -476,13 +441,13 @@
       <c r="E6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5"/>
-      <c r="B7" s="4" t="s">
+    <row r="7" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2"/>
+      <c r="B7" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C7" s="6"/>
@@ -492,11 +457,11 @@
       <c r="E7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="5"/>
-    </row>
-    <row r="8" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5"/>
-      <c r="B8" s="4" t="s">
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2"/>
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6"/>
@@ -506,11 +471,11 @@
       <c r="E8" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="5"/>
-    </row>
-    <row r="9" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5"/>
-      <c r="B9" s="4" t="s">
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2"/>
+      <c r="B9" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C9" s="6"/>
@@ -518,13 +483,13 @@
       <c r="E9" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="5"/>
-    </row>
-    <row r="10" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="6" t="s">
@@ -536,13 +501,13 @@
       <c r="E10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5"/>
-      <c r="B11" s="4" t="s">
+    <row r="11" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2"/>
+      <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="6" t="s">
@@ -554,11 +519,11 @@
       <c r="E11" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F11" s="4"/>
-    </row>
-    <row r="12" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5"/>
-      <c r="B12" s="4" t="s">
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2"/>
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6" t="s">
@@ -570,11 +535,11 @@
       <c r="E12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F12" s="4"/>
-    </row>
-    <row r="13" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5"/>
-      <c r="B13" s="4" t="s">
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="2"/>
+      <c r="B13" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="6"/>
@@ -584,13 +549,13 @@
       <c r="E13" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F13" s="4"/>
-    </row>
-    <row r="14" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="6"/>
@@ -600,45 +565,45 @@
       <c r="E14" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5"/>
-      <c r="B15" s="4" t="s">
+    <row r="15" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="2"/>
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
-      <c r="F15" s="5"/>
-    </row>
-    <row r="16" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5"/>
-      <c r="B16" s="4" t="s">
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="2"/>
+      <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
-      <c r="F16" s="5"/>
-    </row>
-    <row r="17" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5"/>
-      <c r="B17" s="4" t="s">
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="1:6 16384:16384" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="2"/>
+      <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
-      <c r="F17" s="5"/>
-    </row>
-    <row r="18" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="1:6 16384:16384" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C18" s="6" t="s">
@@ -650,13 +615,13 @@
       <c r="E18" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5"/>
-      <c r="B19" s="4" t="s">
+    <row r="19" spans="1:6 16384:16384" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="2"/>
+      <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6" t="s">
@@ -668,11 +633,11 @@
       <c r="E19" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F19" s="4"/>
-    </row>
-    <row r="20" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5"/>
-      <c r="B20" s="4" t="s">
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" spans="1:6 16384:16384" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="2"/>
+      <c r="B20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="6" t="s">
@@ -684,12 +649,12 @@
       <c r="E20" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F20" s="4"/>
+      <c r="F20" s="1"/>
       <c r="XFD20" s="6"/>
     </row>
-    <row r="21" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5"/>
-      <c r="B21" s="4" t="s">
+    <row r="21" spans="1:6 16384:16384" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="2"/>
+      <c r="B21" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="6"/>
@@ -699,13 +664,13 @@
       <c r="E21" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F21" s="4"/>
-    </row>
-    <row r="22" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" spans="1:6 16384:16384" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C22" s="6" t="s">
@@ -717,13 +682,13 @@
       <c r="E22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5"/>
-      <c r="B23" s="4" t="s">
+    <row r="23" spans="1:6 16384:16384" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="2"/>
+      <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="6" t="s">
@@ -735,11 +700,11 @@
       <c r="E23" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F23" s="5"/>
-    </row>
-    <row r="24" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5"/>
-      <c r="B24" s="4" t="s">
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="1:6 16384:16384" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="2"/>
+      <c r="B24" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="6" t="s">
@@ -751,11 +716,11 @@
       <c r="E24" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F24" s="5"/>
-    </row>
-    <row r="25" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5"/>
-      <c r="B25" s="4" t="s">
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" spans="1:6 16384:16384" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="2"/>
+      <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="6"/>
@@ -763,13 +728,13 @@
       <c r="E25" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F25" s="5"/>
-    </row>
-    <row r="26" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="s">
+      <c r="F25" s="2"/>
+    </row>
+    <row r="26" spans="1:6 16384:16384" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C26" s="6" t="s">
@@ -781,13 +746,13 @@
       <c r="E26" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F26" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5"/>
-      <c r="B27" s="4" t="s">
+    <row r="27" spans="1:6 16384:16384" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="2"/>
+      <c r="B27" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C27" s="6" t="s">
@@ -799,11 +764,11 @@
       <c r="E27" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F27" s="5"/>
-    </row>
-    <row r="28" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5"/>
-      <c r="B28" s="4" t="s">
+      <c r="F27" s="2"/>
+    </row>
+    <row r="28" spans="1:6 16384:16384" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="2"/>
+      <c r="B28" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C28" s="6"/>
@@ -813,11 +778,11 @@
       <c r="E28" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F28" s="5"/>
-    </row>
-    <row r="29" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5"/>
-      <c r="B29" s="4" t="s">
+      <c r="F28" s="2"/>
+    </row>
+    <row r="29" spans="1:6 16384:16384" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="2"/>
+      <c r="B29" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="6"/>
@@ -827,13 +792,13 @@
       <c r="E29" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F29" s="5"/>
-    </row>
-    <row r="30" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5" t="s">
+      <c r="F29" s="2"/>
+    </row>
+    <row r="30" spans="1:6 16384:16384" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C30" s="6" t="s">
@@ -845,13 +810,13 @@
       <c r="E30" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="F30" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5"/>
-      <c r="B31" s="4" t="s">
+    <row r="31" spans="1:6 16384:16384" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="2"/>
+      <c r="B31" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="6" t="s">
@@ -863,11 +828,11 @@
       <c r="E31" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F31" s="4"/>
-    </row>
-    <row r="32" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5"/>
-      <c r="B32" s="4" t="s">
+      <c r="F31" s="1"/>
+    </row>
+    <row r="32" spans="1:6 16384:16384" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="2"/>
+      <c r="B32" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C32" s="6" t="s">
@@ -879,11 +844,11 @@
       <c r="E32" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F32" s="4"/>
-    </row>
-    <row r="33" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5"/>
-      <c r="B33" s="4" t="s">
+      <c r="F32" s="1"/>
+    </row>
+    <row r="33" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="2"/>
+      <c r="B33" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="6"/>
@@ -893,13 +858,13 @@
       <c r="E33" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F33" s="4"/>
-    </row>
-    <row r="34" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="5" t="s">
+      <c r="F33" s="1"/>
+    </row>
+    <row r="34" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C34" s="9" t="s">
@@ -911,13 +876,13 @@
       <c r="E34" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="F34" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5"/>
-      <c r="B35" s="4" t="s">
+    <row r="35" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="2"/>
+      <c r="B35" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="9" t="s">
@@ -929,11 +894,11 @@
       <c r="E35" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F35" s="5"/>
-    </row>
-    <row r="36" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="5"/>
-      <c r="B36" s="4" t="s">
+      <c r="F35" s="2"/>
+    </row>
+    <row r="36" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="2"/>
+      <c r="B36" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="9" t="s">
@@ -945,11 +910,11 @@
       <c r="E36" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F36" s="5"/>
-    </row>
-    <row r="37" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5"/>
-      <c r="B37" s="4" t="s">
+      <c r="F36" s="2"/>
+    </row>
+    <row r="37" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="2"/>
+      <c r="B37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="9" t="s">
@@ -961,13 +926,13 @@
       <c r="E37" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F37" s="5"/>
-    </row>
-    <row r="38" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="5" t="s">
+      <c r="F37" s="2"/>
+    </row>
+    <row r="38" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C38" s="9" t="s">
@@ -979,13 +944,13 @@
       <c r="E38" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F38" s="5" t="s">
+      <c r="F38" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="5"/>
-      <c r="B39" s="4" t="s">
+    <row r="39" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="2"/>
+      <c r="B39" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="6"/>
@@ -993,11 +958,11 @@
       <c r="E39" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F39" s="5"/>
-    </row>
-    <row r="40" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="5"/>
-      <c r="B40" s="4" t="s">
+      <c r="F39" s="2"/>
+    </row>
+    <row r="40" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="2"/>
+      <c r="B40" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C40" s="6"/>
@@ -1005,11 +970,11 @@
       <c r="E40" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F40" s="5"/>
-    </row>
-    <row r="41" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="5"/>
-      <c r="B41" s="4" t="s">
+      <c r="F40" s="2"/>
+    </row>
+    <row r="41" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="2"/>
+      <c r="B41" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="6"/>
@@ -1017,13 +982,13 @@
       <c r="E41" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F41" s="5"/>
-    </row>
-    <row r="42" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="5" t="s">
+      <c r="F41" s="2"/>
+    </row>
+    <row r="42" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C42" s="9" t="s">
@@ -1035,13 +1000,13 @@
       <c r="E42" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="F42" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="5"/>
-      <c r="B43" s="4" t="s">
+    <row r="43" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="2"/>
+      <c r="B43" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C43" s="6"/>
@@ -1049,11 +1014,11 @@
       <c r="E43" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F43" s="5"/>
-    </row>
-    <row r="44" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="5"/>
-      <c r="B44" s="4" t="s">
+      <c r="F43" s="2"/>
+    </row>
+    <row r="44" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="2"/>
+      <c r="B44" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="6"/>
@@ -1061,11 +1026,11 @@
       <c r="E44" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F44" s="5"/>
-    </row>
-    <row r="45" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="5"/>
-      <c r="B45" s="4" t="s">
+      <c r="F44" s="2"/>
+    </row>
+    <row r="45" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="2"/>
+      <c r="B45" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C45" s="6"/>
@@ -1073,37 +1038,36 @@
       <c r="E45" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F45" s="5"/>
+      <c r="F45" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A38:A41"/>
+    <mergeCell ref="F38:F41"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="F42:F45"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="F26:F29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="F30:F33"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="F34:F37"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="F18:F21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="F22:F25"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="F2:F5"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="F6:F9"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="F10:F13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="F18:F21"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="F22:F25"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="F26:F29"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="F30:F33"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="F34:F37"/>
-    <mergeCell ref="A38:A41"/>
-    <mergeCell ref="F38:F41"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="F42:F45"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>

--- a/Mandat 1 - Planification/BelleVibe MatricePermissions.xlsx
+++ b/Mandat 1 - Planification/BelleVibe MatricePermissions.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="28">
   <si>
     <t xml:space="preserve">Employés</t>
   </si>
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Delete</t>
   </si>
   <si>
-    <t xml:space="preserve">Seul les superviseurs et les admins peuvent voir les autres employés. Les admins peuvent modifier le statut/position d'un employé (passer de simple employé à superviseur ex). Les superviseurs peuvent modifier les autres infos (ex, changement d'adresse)</t>
+    <t xml:space="preserve">Seul les superviseurs et les admins peuvent voir les autres employés. Les employés ordinaires peuvent utiliser la route /employes/me pour voir les infos de leur compte employé (utilisé surtout pour afficher le nom de l’employé connecté). Les admins peuvent modifier le statut/position d'un employé (passer de simple employé à superviseur ex). Les superviseurs peuvent modifier les autres infos (ex, changement d'adresse)</t>
   </si>
   <si>
     <t xml:space="preserve">Historique des dossiers</t>
@@ -73,13 +73,13 @@
     <t xml:space="preserve">Demandes</t>
   </si>
   <si>
-    <t xml:space="preserve">Les employés devraient seulement écrire et lire les demandes que les clients leur font parvenir. Si on doit en modifier une (ex, l'état de la demande) un superviseur s'en charge. </t>
+    <t xml:space="preserve">Les employés devraient seulement écrire et lire les demandes que les clients leur font parvenir. Si on doit en modifier une (ex, l'état de la demande) un superviseur s'en charge. Aucun delete possible, les demandes completées sont simplement modifiés avec un statut “Résolu”. </t>
   </si>
   <si>
     <t xml:space="preserve">Documents</t>
   </si>
   <si>
-    <t xml:space="preserve">Permissions standard. Pas de delete possibles.</t>
+    <t xml:space="preserve">Permissions standard. Permission de delete donnée seulement aux admins</t>
   </si>
   <si>
     <t xml:space="preserve">Forfait Dossier</t>
@@ -103,7 +103,7 @@
     <t xml:space="preserve">Facturation</t>
   </si>
   <si>
-    <t xml:space="preserve">Permissions standard, sauf que seulement les admins peuvent delete, pas les superviseurs</t>
+    <t xml:space="preserve">Permissions standard, sauf que seulement les admins peuvent delete, pas les superviseurs. Certaines infos plus critiques, comme la date d’emission et le montant à payer sont seulement modifiables par un superviseur.</t>
   </si>
 </sst>
 </file>
@@ -210,31 +210,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -367,7 +367,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.57"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="10.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="2" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="43.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="43.29"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="2" width="10.57"/>
   </cols>
   <sheetData>
@@ -381,7 +381,7 @@
       <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>3</v>
       </c>
       <c r="N1" s="1"/>
@@ -402,7 +402,7 @@
       <c r="E2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>7</v>
       </c>
       <c r="G2" s="6"/>
@@ -422,7 +422,7 @@
       <c r="E3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="3"/>
+      <c r="F3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4"/>
@@ -438,7 +438,7 @@
       <c r="E4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="3"/>
+      <c r="F4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4"/>
@@ -452,7 +452,7 @@
       <c r="E5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="3"/>
+      <c r="F5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
@@ -576,7 +576,7 @@
       <c r="E14" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="4" t="s">
         <v>7</v>
       </c>
     </row>
@@ -594,7 +594,7 @@
       <c r="E15" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F15" s="3"/>
+      <c r="F15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4"/>
@@ -610,7 +610,7 @@
       <c r="E16" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F16" s="3"/>
+      <c r="F16" s="4"/>
       <c r="XFD16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -625,7 +625,7 @@
       <c r="E17" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F17" s="3"/>
+      <c r="F17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
@@ -747,12 +747,8 @@
         <v>10</v>
       </c>
       <c r="C25" s="5"/>
-      <c r="D25" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
       <c r="F25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -771,7 +767,7 @@
       <c r="E26" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F26" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -789,7 +785,7 @@
       <c r="E27" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F27" s="3"/>
+      <c r="F27" s="4"/>
     </row>
     <row r="28" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4"/>
@@ -805,7 +801,7 @@
       <c r="E28" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F28" s="3"/>
+      <c r="F28" s="4"/>
     </row>
     <row r="29" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4"/>
@@ -814,8 +810,10 @@
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="3"/>
+      <c r="E29" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F29" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
